--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_356_India_mainland.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_356_India_mainland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R10f7905e991d4dbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R177ab74cb6f8401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ref2d6f08272a4ce3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd0c65e16a4ae4057"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb46b02f51ce04874"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rdbb481b5c113444c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R21b7cd0346cd4097"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R91cc3ef46ac74544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd17828ec34764ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R676f689002164362"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5578303e3b884eca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R62727897bdcd4e80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ356CommercialTable" displayName="EEZ356CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ356CommercialTable" displayName="EEZ356CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ356FunctionalTable" displayName="EEZ356FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ356FunctionalTable" displayName="EEZ356FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ356ValidationTable" displayName="EEZ356ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ356ValidationTable" displayName="EEZ356ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10811,7 +10765,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra53979d4862b4cfe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd52915bf11844a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10821,20 +10775,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10842,660 +10786,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>167472.3348419496</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.3419098221132044</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>219.74035515758175</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>167472.3348419496</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>225.2156849978336</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$152,A2,'Species'!$U$2:$U$152))</x:f>
-        <x:v>37717396.609616235</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.3419098221132044</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>219.74035515758175</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>36800430.33723946</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>916966.2723767757</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0249172703681366</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.024917270368136703</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>228.4255138298</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>199.52623149688787</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>228.4255138298</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$152,A3,'Species'!$U$2:$U$152))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>45576.88195220024</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>45576.88195220024</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>452226.1909589784</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.3698300187427503</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>234.33114723481182</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>452226.1909589784</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>236.9383594922799</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$152,A4,'Species'!$U$2:$U$152))</x:f>
-        <x:v>107149731.80526283</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.3698300187427503</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>234.33114723481182</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>105970682.13704649</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1179049.6682163477</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0111261873986197</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.01112618739861977</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>47754.494267179994</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.151271160869112</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>141.66780365232427</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>47754.494267179994</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>141.99380287673836</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$152,A5,'Species'!$U$2:$U$152))</x:f>
-        <x:v>6780842.245452289</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.151271160869112</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>141.66780365232427</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>6765274.3173589</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>15567.928093388677</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0023011525273178</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.002301152527317806</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>545218.4776801894</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.724644356656049</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>53.04498814132957</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>545218.4776801894</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>183.85419718745447</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$152,A6,'Species'!$U$2:$U$152))</x:f>
-        <x:v>100240705.50565729</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.724644356656049</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>53.04498814132957</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>28921107.68297941</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>71319597.82267788</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>3.4660050577748356</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>2.4660050577748356</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>96995.2196248261</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.238761410322855</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>17.328517541840604</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>96995.2196248261</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>19.313125779867335</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$152,A7,'Species'!$U$2:$U$152))</x:f>
-        <x:v>1873280.876660123</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.238761410322855</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>17.328517541840604</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1680783.3647434812</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>192497.51191664184</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.114528449028302</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.11452844902830207</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1344582.4540375255</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5298486130154596</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>338.72606194808776</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1344582.4540375255</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>549.5469016879035</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$152,A8,'Species'!$U$2:$U$152))</x:f>
-        <x:v>738911121.68024</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5298486130154596</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>338.72606194808776</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>455445119.6206267</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>283466002.05961335</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.622393324349886</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.622393324349886</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1570891.6737897792</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6450404039158717</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>441.61153008838875</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1570891.6737897792</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>666.8608971306555</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$152,A9,'Species'!$U$2:$U$152))</x:f>
-        <x:v>1047566230.8785293</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6450404039158717</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>441.61153008838875</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>693723875.6654145</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>353842355.21311486</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.5100622418014835</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5100622418014834</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>190.26734009979998</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>190.26734009979998</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$152,A10,'Species'!$U$2:$U$152))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>151134.72038715857</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>151134.72038715857</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>54460.7937534232</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.9183369042499647</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>828.584689616225</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>54460.7937534232</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>959.1772538843139</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$152,A11,'Species'!$U$2:$U$152))</x:f>
-        <x:v>52237554.59676846</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.9183369042499647</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>828.584689616225</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>45125379.888433404</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>7112174.708335057</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1576091930066623</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.1576091930066623</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>64011.86712507719</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.392122321012395</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2466.7340062324974</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>64011.86712507719</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2526.117806558251</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$152,A12,'Species'!$U$2:$U$152))</x:f>
-        <x:v>161701517.37569818</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.392122321012395</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2466.7340062324974</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>157900249.43986395</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>3801267.935834229</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0240738564335323</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.024073856433532333</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d3f40ed21544589"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52d098ffb397452f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11505,20 +11020,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11526,1146 +11031,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>217605.20876812417</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8729197554785926</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>746.310849934368</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>217605.20876812417</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>880.5884862436798</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$152,A2,'Species'!$U$2:$U$152))</x:f>
-        <x:v>191620641.38786238</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8729197554785926</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>746.310849934368</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>162401128.30588433</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>29219513.081978053</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.179921860068255</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.17992186006825503</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>13681.700752133798</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>13681.700752133798</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$152,A3,'Species'!$U$2:$U$152))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3945845.598550485</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>3945845.598550485</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>11008.000419710901</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.153081198450716</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1422.5947395948483</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>11008.000419710901</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1427.6550387256323</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$152,A4,'Species'!$U$2:$U$152))</x:f>
-        <x:v>15715627.265494144</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.153081198450716</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1422.5947395948483</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>15659923.49053861</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>55703.774955533445</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0035570911306935</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0035570911306934848</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>15237.4896526693</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.99820376694069</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>995.8725619174409</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>15237.4896526693</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1120.3149582702347</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$152,A5,'Species'!$U$2:$U$152))</x:f>
-        <x:v>17070787.58437334</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.99820376694069</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>995.8725619174409</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>15174597.85759427</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1896189.7267790698</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.124958153393838</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.12495815339383796</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>193215.83524252227</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.412356896610531</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2584.3831250261705</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>193215.83524252227</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2617.3274867780865</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$152,A6,'Species'!$U$2:$U$152))</x:f>
-        <x:v>505709116.4610396</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.412356896610531</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2584.3831250261705</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>499343744.0886114</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>6365372.372428179</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0127474759577615</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.012747475957761488</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>27009.331147087905</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.7199799038725576</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>524.7831763731969</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>27009.331147087905</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>524.788169074378</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$152,A7,'Species'!$U$2:$U$152))</x:f>
-        <x:v>14174177.44060383</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.7199799038725576</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>524.7831763731969</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>14174042.59108431</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>134.84951951913536</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.000009513836201</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.000009513836201110173</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>25.9278213681</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>25.9278213681</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$152,A8,'Species'!$U$2:$U$152))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>81990.97028917898</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>81990.97028917898</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>27451.4626063353</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.11349917976748</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1298.6711110849353</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>27451.4626063353</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1386.570096537599</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$152,A9,'Species'!$U$2:$U$152))</x:f>
-        <x:v>38063377.156164624</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.11349917976748</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1298.6711110849353</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>35650421.44387602</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2412955.712288603</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0676837920720597</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.06768379207205971</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>235564.43169531223</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.429395201224849</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>268.7789179510648</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>235564.43169531223</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>269.0002072960763</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$152,A10,'Species'!$U$2:$U$152))</x:f>
-        <x:v>63366880.9576214</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.429395201224849</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>268.7789179510648</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>63314753.05882353</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>52127.89879786968</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0008233136240685</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0008233136240686189</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>178095.3852432857</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.958797768554374</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>909.4896655004113</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>178095.3852432857</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1229.657081360339</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$152,A11,'Species'!$U$2:$U$152))</x:f>
-        <x:v>218996251.62200388</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.958797768554374</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>909.4896655004113</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>161975912.35208282</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>57020339.269921064</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.3520297459166486</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.35202974591664865</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1019282.209691233</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.485950363394451</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>306.16134942085347</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1019282.209691233</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>418.2734116411266</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$152,A12,'Species'!$U$2:$U$152))</x:f>
-        <x:v>426338647.2726582</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.485950363394451</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>306.16134942085347</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>312064816.7597372</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>114273830.51292104</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3661862035568781</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.36618620355687825</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>742375.8896053452</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.5261652327632294</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>335.86537411654876</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>742375.8896053452</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>588.305794725108</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$152,A13,'Species'!$U$2:$U$152))</x:f>
-        <x:v>436744037.7190316</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.5261652327632294</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>335.86537411654876</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>249338355.89740497</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>187405681.8216266</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.7516119256787681</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.7516119256787682</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>134687.23007185137</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.6507122935493546</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>447.4168063985964</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>134687.23007185137</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>580.3113066015611</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$152,A14,'Species'!$U$2:$U$152))</x:f>
-        <x:v>78160522.46554114</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.6507122935493546</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>447.4168063985964</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>60261330.34142074</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>17899192.1241204</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.297026169563624</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.29702616956362404</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>99353.6071511873</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.2331301573508804</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>17.10527880706656</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>99353.6071511873</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>19.0934852215746</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$152,A15,'Species'!$U$2:$U$152))</x:f>
-        <x:v>1897006.6298513233</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.2331301573508804</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>17.10527880706656</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>1699471.150808821</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>197535.47904250235</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.1162334994321559</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.11623349943215586</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>216661.75926366623</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.3050680671740476</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>201.8682727962075</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>216661.75926366623</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>202.0792732249532</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$152,A16,'Species'!$U$2:$U$152))</x:f>
-        <x:v>43782850.847641446</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.3050680671740476</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>201.8682727962075</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>43737135.12354401</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>45715.72409743816</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.001045238193318</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.0010452381933179948</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>108411.5874385319</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.2584879376437725</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>181.33763093667432</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>108411.5874385319</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>185.60697716776934</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$152,A17,'Species'!$U$2:$U$152))</x:f>
-        <x:v>20121947.03442522</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.2584879376437725</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>181.33763093667432</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>19659100.432187494</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>462846.6022377275</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0235436307899377</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.023543630789937722</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>188642.69546747103</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.5192302638368025</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>330.5447500980055</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>188642.69546747103</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>331.4208851834192</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$152,A18,'Species'!$U$2:$U$152))</x:f>
-        <x:v>62520129.115215436</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.5192302638368025</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>330.5447500980055</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>62354852.63110937</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>165276.48410606384</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.002650579339572</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.002650579339571817</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>867922.1176754625</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.9506360210176656</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>89.25571246775894</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>867922.1176754625</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>125.90446297158051</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$152,A19,'Species'!$U$2:$U$152))</x:f>
-        <x:v>109275268.12708601</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.9506360210176656</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>89.25571246775894</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>77467006.97964951</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>31808261.1474365</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.4106039769394019</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.410603976939402</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>45.8349523801</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>199.52623149688787</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>45.8349523801</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>199.52623149688785</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$152,A20,'Species'!$U$2:$U$152))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>9145.275319240664</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>9145.275319240664</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>47754.494267179994</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.151271160869112</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>141.66780365232427</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>47754.494267179994</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>141.99380287673836</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$152,A21,'Species'!$U$2:$U$152))</x:f>
-        <x:v>6780842.245452289</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.151271160869112</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>141.66780365232427</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>6765274.3173589</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>15567.928093388677</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0023011525273178</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.002301152527317806</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5040945cc5a24c0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0daa1f07ae0c4a24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12840,7 +11601,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -12939,7 +11700,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>2254375093.176224</x:v>
+        <x:v>1532529614.0560458</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12953,7 +11714,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>2254375093.1762247</x:v>
+        <x:v>1805078848.6658754</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12967,7 +11728,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-4.76837158203125e-7</x:v>
+        <x:v>-721845479.1201789</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12981,7 +11742,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-449296244.5103493</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12992,9 +11753,9 @@
         <x:v>EEZ_356</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13006,47 +11767,19 @@
         <x:v>EEZ_356</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_356</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_356</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R314ebf70926448f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89c636bc12e44766"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13093,7 +11826,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
